--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:56</t>
+    <t xml:space="preserve">2026-09-24 00:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G14" s="2"/>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G26" s="2"/>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G29" s="2"/>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="G39" s="2"/>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G40" s="2"/>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G43" s="2"/>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="G44" s="2"/>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G54" s="2"/>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G56" s="2"/>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="G59" s="2"/>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G68" s="2"/>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G69" s="2"/>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G71" s="2"/>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G83" s="2"/>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G84" s="2"/>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="G99" s="2"/>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G100" s="2"/>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G101" s="2"/>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="n">
-        <v>0.13</v>
+        <v>0.07</v>
       </c>
       <c r="G103" s="2"/>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="G104" s="2"/>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G116" s="2"/>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G118" s="2"/>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G119" s="2"/>
     </row>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_arica_y_parinacota.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:47</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
